--- a/jpcore-r4/main/StructureDefinition-jp-medication.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medication.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="278">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -317,16 +317,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -452,7 +452,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -625,85 +625,81 @@
     <t>比率（Ratio)を表すデータ型は、量(Quantity)と共通単位を使って適切に表現できないときのみに使われるべきである。分母が"1"に固定されているとわかっているような場合は、量(Quantity)を比率(Ratio)の代わりに使うべきである。</t>
   </si>
   <si>
+    <t>.quantity</t>
+  </si>
+  <si>
+    <t>Medication.ingredient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>薬効がある、あるいは薬効を伴わない成分</t>
+  </si>
+  <si>
+    <t>この薬剤を構成する特定の重要成分を識別する</t>
+  </si>
+  <si>
+    <t>すべての成分を含む必要はない。もし、ある成分が記載されていなくてもその成分が含有されているかどうかを必ずしも意味しない。特定の成分が記載されていても、すべての成分が記載されていると言うことを意味しない。有効成分であるか、有効成分ではないかを指定することは可能である。</t>
+  </si>
+  <si>
+    <t>.scopesRole[typeCode=INGR]</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.extension:drugNo</t>
+  </si>
+  <si>
+    <t>drugNo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Medication_Ingredient_DrugNo}
+</t>
+  </si>
+  <si>
+    <t>RP内の薬剤の連番</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-rat-1:分子と分母の両方が存在するか、両方が存在します。両方が欠席している場合、いくつかの拡張が存在するものとします / Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.empty() xor denominator.exists()) and (numerator.exists() or extension.exists())}</t>
-  </si>
-  <si>
-    <t>RTO</t>
-  </si>
-  <si>
-    <t>Medication.ingredient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>薬効がある、あるいは薬効を伴わない成分</t>
-  </si>
-  <si>
-    <t>この薬剤を構成する特定の重要成分を識別する</t>
-  </si>
-  <si>
-    <t>すべての成分を含む必要はない。もし、ある成分が記載されていなくてもその成分が含有されているかどうかを必ずしも意味しない。特定の成分が記載されていても、すべての成分が記載されていると言うことを意味しない。有効成分であるか、有効成分ではないかを指定することは可能である。</t>
-  </si>
-  <si>
-    <t>.scopesRole[typeCode=INGR]</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.extension:drugNo</t>
-  </si>
-  <si>
-    <t>drugNo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Medication_Ingredient_DrugNo}
-</t>
-  </si>
-  <si>
-    <t>RP内の薬剤の連番</t>
   </si>
   <si>
     <t>Medication.ingredient.modifierExtension</t>
@@ -775,7 +771,13 @@
     <t>この薬剤中にどの程度の物質が含まれているかを示す。たとえば、1錠あたり250mgなど。これは分子が250mgで分母が1錠である比率を表現している。</t>
   </si>
   <si>
-    <t>Ratioデータ型は2つの数字の関係で示され、Quantityや一般的な単位で適切に表現できない関係を表すときにのみ用いられる。分母の値が「1」で固定されているような値であれば、QuantityがRatioの代わりに用いられるべきである。</t>
+    <t>1回に使用される薬剤量を示すため、denominatorは1回に固定される。</t>
+  </si>
+  <si>
+    <t>//element(*,DrugCodedType)/Strength</t>
+  </si>
+  <si>
+    <t>RXC-3-Component Amount &amp; RXC-4-Component Units  if medication: RXO-2-Requested Give Amount - Minimum &amp; RXO-4-Requested Give Units / RXO-3-Requested Give Amount - Maximum &amp; RXO-4-Requested Give Units / RXO-11-Requested Dispense Amount &amp; RXO-12-Requested Dispense Units / RXE-3-Give Amount - Minimum &amp; RXE-5-Give Units / RXE-4-Give Amount - Maximum &amp; RXE-5-Give Units / RXE-10-Dispense Amount &amp; RXE-10-Dispense Units</t>
   </si>
   <si>
     <t>Medication.ingredient.strength.id</t>
@@ -816,23 +818,13 @@
     <t>投与量</t>
   </si>
   <si>
-    <t>薬剤に関する数量と単位を定めたデータイプ</t>
-  </si>
-  <si>
-    <t>薬剤に関する数量と単位を定めている。ValueおよびCodeを必須としている。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
+    <t>分子の値。 / The value of the numerator.</t>
   </si>
   <si>
     <t>Ratio.numerator</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>.numerator</t>
   </si>
   <si>
     <t>Medication.ingredient.strength.denominator</t>
@@ -841,7 +833,21 @@
     <t>パッケージ量</t>
   </si>
   <si>
+    <t>分母の値。 / The value of the denominator.</t>
+  </si>
+  <si>
+    <t>&lt;valueQuantity xmlns="http://hl7.org/fhir"&gt;
+  &lt;value value="1"/&gt;
+  &lt;unit value="回"/&gt;
+  &lt;system value="http://jpfhir.jp/fhir/core/mhlw/CodeSystem/MedicationUnitMERIT9Code"/&gt;
+  &lt;code value="TIME"/&gt;
+&lt;/valueQuantity&gt;</t>
+  </si>
+  <si>
     <t>Ratio.denominator</t>
+  </si>
+  <si>
+    <t>.denominator</t>
   </si>
   <si>
     <t>Medication.batch</t>
@@ -1241,7 +1247,7 @@
     <col min="37" max="37" width="195.5390625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.9296875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="173.4375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2981,7 +2987,7 @@
         <v>78</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>187</v>
@@ -3052,30 +3058,30 @@
         <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>193</v>
-      </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3098,16 +3104,16 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3157,7 +3163,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3175,7 +3181,7 @@
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -3186,10 +3192,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3212,13 +3218,13 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3269,7 +3275,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3287,7 +3293,7 @@
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -3298,10 +3304,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3327,10 +3333,10 @@
         <v>134</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3369,17 +3375,17 @@
         <v>78</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3408,13 +3414,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>78</v>
@@ -3436,13 +3442,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3493,7 +3499,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3502,7 +3508,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>139</v>
@@ -3522,14 +3528,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3551,10 +3557,10 @@
         <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>137</v>
@@ -3609,7 +3615,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3638,10 +3644,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3667,16 +3673,16 @@
         <v>152</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -3725,7 +3731,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>88</v>
@@ -3743,21 +3749,21 @@
         <v>158</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>227</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3780,17 +3786,17 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -3839,7 +3845,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3857,7 +3863,7 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -3868,10 +3874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3897,13 +3903,13 @@
         <v>187</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3953,7 +3959,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3962,30 +3968,30 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AJ24" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>193</v>
-      </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>131</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4008,13 +4014,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4065,7 +4071,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4083,7 +4089,7 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4094,10 +4100,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4126,7 +4132,7 @@
         <v>135</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>137</v>
@@ -4167,19 +4173,19 @@
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4197,7 +4203,7 @@
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4208,13 +4214,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>78</v>
@@ -4236,13 +4242,13 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4293,7 +4299,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4322,10 +4328,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4345,20 +4351,18 @@
         <v>78</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N28" t="s" s="2">
         <v>251</v>
       </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -4416,30 +4420,30 @@
         <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AK28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>254</v>
-      </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>255</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4459,20 +4463,18 @@
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -4482,7 +4484,7 @@
         <v>78</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>78</v>
+        <v>257</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>78</v>
@@ -4530,30 +4532,30 @@
         <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>253</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>255</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4576,13 +4578,13 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4633,7 +4635,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4651,7 +4653,7 @@
         <v>174</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -4662,10 +4664,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4688,13 +4690,13 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4745,7 +4747,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -4763,7 +4765,7 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -4774,10 +4776,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4806,7 +4808,7 @@
         <v>135</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>137</v>
@@ -4859,7 +4861,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -4877,7 +4879,7 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -4888,14 +4890,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4917,10 +4919,10 @@
         <v>134</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>137</v>
@@ -4975,7 +4977,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5004,10 +5006,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5030,16 +5032,16 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5089,7 +5091,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5113,15 +5115,15 @@
         <v>78</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5144,13 +5146,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5201,7 +5203,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5219,13 +5221,13 @@
         <v>174</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/main/StructureDefinition-jp-medication.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medication.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -270,7 +270,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>NewRx/MedicationPrescribed@@ -536,7 +536,7 @@
     <t>Medication.status</t>
   </si>
   <si>
-    <t>アクティブ|非アクティブ|エラーに入った / active | inactive | entered-in-error</t>
+    <t>アクティブ|非アクティブ|エラー入力 / active | inactive | entered-in-error</t>
   </si>
   <si>
     <t>薬剤が有効に使われているかどうかを指定するコード。</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medication.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medication.xlsx
@@ -1209,17 +1209,17 @@
   <dimension ref="A1:AN35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.82421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.73046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.4296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.77734375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.40625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="106.484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="91.2890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1228,25 +1228,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="92.3828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.87890625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="79.203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.48046875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="195.5390625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="98.9296875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="167.640625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="84.81640625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/jpcore-r4/main/StructureDefinition-jp-medication.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medication.xlsx
@@ -371,7 +371,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medication.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medication.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
